--- a/Result/profitability/4304.xlsx
+++ b/Result/profitability/4304.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.32</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3100000000000001</v>
+        <v>-0.2575</v>
       </c>
       <c r="N2" t="n">
-        <v>6.606249999999999</v>
+        <v>9.515000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.26</v>
+        <v>-0.19</v>
       </c>
       <c r="N3" t="n">
-        <v>7.88375</v>
+        <v>11.16</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>-0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.22375</v>
+        <v>-0.15625</v>
       </c>
       <c r="N4" t="n">
-        <v>9.1425</v>
+        <v>11.97125</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.73</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2575</v>
+        <v>-0.19375</v>
       </c>
       <c r="N5" t="n">
-        <v>8.776249999999999</v>
+        <v>11.6675</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.23875</v>
+        <v>-0.21125</v>
       </c>
       <c r="N6" t="n">
-        <v>9.565</v>
+        <v>10.92125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.22</v>
+        <v>-0.1875</v>
       </c>
       <c r="N7" t="n">
-        <v>9.12875</v>
+        <v>11.74625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.175</v>
+        <v>-0.14875</v>
       </c>
       <c r="N8" t="n">
-        <v>10.17125</v>
+        <v>11.6775</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1645,7 +1645,7 @@
         <v>0.12</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07750000000000001</v>
+        <v>-0.0775</v>
       </c>
       <c r="N10" t="n">
         <v>10.84375</v>
@@ -1772,7 +1772,7 @@
         <v>-0.03</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.08875000000000001</v>
+        <v>-0.08875</v>
       </c>
       <c r="N11" t="n">
         <v>10.69625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>95</v>
+      </c>
+      <c r="D75" t="n">
+        <v>70</v>
+      </c>
+      <c r="E75" t="n">
+        <v>25</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>9</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.98%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.744999999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.615384615384615</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.8558238636363635</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.186046511627907</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>23.13</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>7.709999999999999</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
